--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T4_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T4_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>45</t>
+    <t>56</t>
+  </si>
+  <si>
+    <t>55</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.53e+05</t>
-  </si>
-  <si>
-    <t>(94122.672)</t>
-  </si>
-  <si>
-    <t>493.915</t>
-  </si>
-  <si>
-    <t>(38.553)</t>
-  </si>
-  <si>
-    <t>3.759</t>
-  </si>
-  <si>
-    <t>(0.053)</t>
-  </si>
-  <si>
-    <t>4.870</t>
-  </si>
-  <si>
-    <t>(1.337)</t>
-  </si>
-  <si>
-    <t>86.367</t>
-  </si>
-  <si>
-    <t>(0.550)</t>
-  </si>
-  <si>
-    <t>8.40e+05</t>
-  </si>
-  <si>
-    <t>(59329.455)</t>
-  </si>
-  <si>
-    <t>2.002</t>
-  </si>
-  <si>
-    <t>(0.150)</t>
-  </si>
-  <si>
-    <t>1.957</t>
-  </si>
-  <si>
-    <t>(0.453)</t>
-  </si>
-  <si>
-    <t>29.783</t>
-  </si>
-  <si>
-    <t>(5.444)</t>
-  </si>
-  <si>
-    <t>0.913</t>
-  </si>
-  <si>
-    <t>(0.042)</t>
-  </si>
-  <si>
-    <t>70</t>
+    <t>5.24e+05</t>
+  </si>
+  <si>
+    <t>(80953.804)</t>
+  </si>
+  <si>
+    <t>503.534</t>
+  </si>
+  <si>
+    <t>(38.331)</t>
+  </si>
+  <si>
+    <t>3.714</t>
+  </si>
+  <si>
+    <t>(0.049)</t>
+  </si>
+  <si>
+    <t>6.411</t>
+  </si>
+  <si>
+    <t>(1.336)</t>
+  </si>
+  <si>
+    <t>87.003</t>
+  </si>
+  <si>
+    <t>(0.512)</t>
+  </si>
+  <si>
+    <t>8.97e+05</t>
+  </si>
+  <si>
+    <t>(55836.359)</t>
+  </si>
+  <si>
+    <t>2.162</t>
+  </si>
+  <si>
+    <t>(0.135)</t>
+  </si>
+  <si>
+    <t>2.339</t>
+  </si>
+  <si>
+    <t>(0.404)</t>
+  </si>
+  <si>
+    <t>29.286</t>
+  </si>
+  <si>
+    <t>(4.490)</t>
+  </si>
+  <si>
+    <t>0.929</t>
+  </si>
+  <si>
+    <t>(0.035)</t>
+  </si>
+  <si>
+    <t>60</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.54e+05</t>
-  </si>
-  <si>
-    <t>(88832.584)</t>
-  </si>
-  <si>
-    <t>491.794</t>
-  </si>
-  <si>
-    <t>(41.353)</t>
-  </si>
-  <si>
-    <t>3.360</t>
-  </si>
-  <si>
-    <t>(0.044)</t>
-  </si>
-  <si>
-    <t>23.357</t>
-  </si>
-  <si>
-    <t>(2.818)</t>
-  </si>
-  <si>
-    <t>91.285</t>
-  </si>
-  <si>
-    <t>(0.345)</t>
-  </si>
-  <si>
-    <t>1.35e+06</t>
-  </si>
-  <si>
-    <t>(52871.911)</t>
-  </si>
-  <si>
-    <t>3.285</t>
-  </si>
-  <si>
-    <t>(0.107)</t>
-  </si>
-  <si>
-    <t>5.786</t>
-  </si>
-  <si>
-    <t>(0.482)</t>
-  </si>
-  <si>
-    <t>41.743</t>
-  </si>
-  <si>
-    <t>(2.481)</t>
+    <t>6.98e+05</t>
+  </si>
+  <si>
+    <t>(1.00e+05)</t>
+  </si>
+  <si>
+    <t>482.463</t>
+  </si>
+  <si>
+    <t>(43.823)</t>
+  </si>
+  <si>
+    <t>3.335</t>
+  </si>
+  <si>
+    <t>(0.048)</t>
+  </si>
+  <si>
+    <t>25.000</t>
+  </si>
+  <si>
+    <t>(3.191)</t>
+  </si>
+  <si>
+    <t>91.511</t>
+  </si>
+  <si>
+    <t>(0.367)</t>
+  </si>
+  <si>
+    <t>1.38e+06</t>
+  </si>
+  <si>
+    <t>(57218.217)</t>
+  </si>
+  <si>
+    <t>3.352</t>
+  </si>
+  <si>
+    <t>(0.119)</t>
+  </si>
+  <si>
+    <t>6.067</t>
+  </si>
+  <si>
+    <t>(0.544)</t>
+  </si>
+  <si>
+    <t>44.200</t>
+  </si>
+  <si>
+    <t>(2.738)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.00e+05</t>
-  </si>
-  <si>
-    <t>-2.121</t>
-  </si>
-  <si>
-    <t>-0.399***</t>
-  </si>
-  <si>
-    <t>18.488***</t>
-  </si>
-  <si>
-    <t>4.918***</t>
-  </si>
-  <si>
-    <t>5.07e+05***</t>
-  </si>
-  <si>
-    <t>1.283***</t>
-  </si>
-  <si>
-    <t>3.829***</t>
-  </si>
-  <si>
-    <t>11.960**</t>
-  </si>
-  <si>
-    <t>0.087**</t>
+    <t>1.74e+05</t>
+  </si>
+  <si>
+    <t>-21.071</t>
+  </si>
+  <si>
+    <t>-0.380***</t>
+  </si>
+  <si>
+    <t>18.589***</t>
+  </si>
+  <si>
+    <t>4.508***</t>
+  </si>
+  <si>
+    <t>4.82e+05***</t>
+  </si>
+  <si>
+    <t>1.190***</t>
+  </si>
+  <si>
+    <t>3.727***</t>
+  </si>
+  <si>
+    <t>14.914***</t>
+  </si>
+  <si>
+    <t>0.071**</t>
   </si>
 </sst>
 </file>

--- a/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T4_2.xlsx
+++ b/data/controles_results/dif_medias/controls_vars/difmedias_controles_baselines_fixed_2023_T4_2.xlsx
@@ -57,10 +57,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>55</t>
+    <t>46</t>
+  </si>
+  <si>
+    <t>45</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -72,67 +72,67 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.24e+05</t>
-  </si>
-  <si>
-    <t>(80953.804)</t>
-  </si>
-  <si>
-    <t>503.534</t>
-  </si>
-  <si>
-    <t>(38.331)</t>
-  </si>
-  <si>
-    <t>3.714</t>
-  </si>
-  <si>
-    <t>(0.049)</t>
-  </si>
-  <si>
-    <t>6.411</t>
-  </si>
-  <si>
-    <t>(1.336)</t>
-  </si>
-  <si>
-    <t>87.003</t>
-  </si>
-  <si>
-    <t>(0.512)</t>
-  </si>
-  <si>
-    <t>8.97e+05</t>
-  </si>
-  <si>
-    <t>(55836.359)</t>
-  </si>
-  <si>
-    <t>2.162</t>
-  </si>
-  <si>
-    <t>(0.135)</t>
-  </si>
-  <si>
-    <t>2.339</t>
-  </si>
-  <si>
-    <t>(0.404)</t>
-  </si>
-  <si>
-    <t>29.286</t>
-  </si>
-  <si>
-    <t>(4.490)</t>
-  </si>
-  <si>
-    <t>0.929</t>
-  </si>
-  <si>
-    <t>(0.035)</t>
-  </si>
-  <si>
-    <t>60</t>
+    <t>5.53e+05</t>
+  </si>
+  <si>
+    <t>(94122.672)</t>
+  </si>
+  <si>
+    <t>493.915</t>
+  </si>
+  <si>
+    <t>(38.553)</t>
+  </si>
+  <si>
+    <t>3.759</t>
+  </si>
+  <si>
+    <t>(0.053)</t>
+  </si>
+  <si>
+    <t>4.870</t>
+  </si>
+  <si>
+    <t>(1.337)</t>
+  </si>
+  <si>
+    <t>86.367</t>
+  </si>
+  <si>
+    <t>(0.550)</t>
+  </si>
+  <si>
+    <t>8.40e+05</t>
+  </si>
+  <si>
+    <t>(59329.455)</t>
+  </si>
+  <si>
+    <t>2.002</t>
+  </si>
+  <si>
+    <t>(0.150)</t>
+  </si>
+  <si>
+    <t>1.957</t>
+  </si>
+  <si>
+    <t>(0.453)</t>
+  </si>
+  <si>
+    <t>29.783</t>
+  </si>
+  <si>
+    <t>(5.444)</t>
+  </si>
+  <si>
+    <t>0.913</t>
+  </si>
+  <si>
+    <t>(0.042)</t>
+  </si>
+  <si>
+    <t>70</t>
   </si>
   <si>
     <t xml:space="preserve"> (2) </t>
@@ -141,58 +141,58 @@
     <t>1</t>
   </si>
   <si>
-    <t>6.98e+05</t>
-  </si>
-  <si>
-    <t>(1.00e+05)</t>
-  </si>
-  <si>
-    <t>482.463</t>
-  </si>
-  <si>
-    <t>(43.823)</t>
-  </si>
-  <si>
-    <t>3.335</t>
-  </si>
-  <si>
-    <t>(0.048)</t>
-  </si>
-  <si>
-    <t>25.000</t>
-  </si>
-  <si>
-    <t>(3.191)</t>
-  </si>
-  <si>
-    <t>91.511</t>
-  </si>
-  <si>
-    <t>(0.367)</t>
-  </si>
-  <si>
-    <t>1.38e+06</t>
-  </si>
-  <si>
-    <t>(57218.217)</t>
-  </si>
-  <si>
-    <t>3.352</t>
-  </si>
-  <si>
-    <t>(0.119)</t>
-  </si>
-  <si>
-    <t>6.067</t>
-  </si>
-  <si>
-    <t>(0.544)</t>
-  </si>
-  <si>
-    <t>44.200</t>
-  </si>
-  <si>
-    <t>(2.738)</t>
+    <t>6.54e+05</t>
+  </si>
+  <si>
+    <t>(88832.584)</t>
+  </si>
+  <si>
+    <t>491.794</t>
+  </si>
+  <si>
+    <t>(41.353)</t>
+  </si>
+  <si>
+    <t>3.360</t>
+  </si>
+  <si>
+    <t>(0.044)</t>
+  </si>
+  <si>
+    <t>23.357</t>
+  </si>
+  <si>
+    <t>(2.818)</t>
+  </si>
+  <si>
+    <t>91.285</t>
+  </si>
+  <si>
+    <t>(0.345)</t>
+  </si>
+  <si>
+    <t>1.35e+06</t>
+  </si>
+  <si>
+    <t>(52871.911)</t>
+  </si>
+  <si>
+    <t>3.285</t>
+  </si>
+  <si>
+    <t>(0.107)</t>
+  </si>
+  <si>
+    <t>5.786</t>
+  </si>
+  <si>
+    <t>(0.482)</t>
+  </si>
+  <si>
+    <t>41.743</t>
+  </si>
+  <si>
+    <t>(2.481)</t>
   </si>
   <si>
     <t>1.000</t>
@@ -216,34 +216,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.74e+05</t>
-  </si>
-  <si>
-    <t>-21.071</t>
-  </si>
-  <si>
-    <t>-0.380***</t>
-  </si>
-  <si>
-    <t>18.589***</t>
-  </si>
-  <si>
-    <t>4.508***</t>
-  </si>
-  <si>
-    <t>4.82e+05***</t>
-  </si>
-  <si>
-    <t>1.190***</t>
-  </si>
-  <si>
-    <t>3.727***</t>
-  </si>
-  <si>
-    <t>14.914***</t>
-  </si>
-  <si>
-    <t>0.071**</t>
+    <t>1.00e+05</t>
+  </si>
+  <si>
+    <t>-2.121</t>
+  </si>
+  <si>
+    <t>-0.399***</t>
+  </si>
+  <si>
+    <t>18.488***</t>
+  </si>
+  <si>
+    <t>4.918***</t>
+  </si>
+  <si>
+    <t>5.07e+05***</t>
+  </si>
+  <si>
+    <t>1.283***</t>
+  </si>
+  <si>
+    <t>3.829***</t>
+  </si>
+  <si>
+    <t>11.960**</t>
+  </si>
+  <si>
+    <t>0.087**</t>
   </si>
 </sst>
 </file>
